--- a/Test_Tracker.xlsx
+++ b/Test_Tracker.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Tracker July" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tracker August" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tracker September" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -48,7 +49,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +136,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
         <bgColor rgb="FFBFBFBF"/>
       </patternFill>
@@ -147,8 +154,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BFBFBF"/>
-        <bgColor rgb="00BFBFBF"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,10 +233,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1695,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA56"/>
+  <dimension ref="A1:AH77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="26.6328125" customWidth="1" min="1" max="2"/>
@@ -1711,112 +1722,154 @@
     <col width="17.1796875" customWidth="1" min="12" max="12"/>
     <col width="28.6328125" customWidth="1" min="13" max="13"/>
     <col width="23.7265625" customWidth="1" min="14" max="14"/>
+    <col width="14.54296875" customWidth="1" min="17" max="17"/>
+    <col width="18.36328125" customWidth="1" min="19" max="19"/>
+    <col width="15.54296875" customWidth="1" min="20" max="20"/>
     <col width="16.36328125" customWidth="1" min="21" max="21"/>
     <col width="17.453125" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="I1" s="24" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="24" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="L1" s="24" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="M1" s="24" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="N1" s="24" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="O1" s="24" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="P1" s="22" t="inlineStr">
+      <c r="P1" s="24" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="R1" s="22" t="n"/>
-      <c r="S1" s="22" t="n"/>
-      <c r="T1" s="22" t="n"/>
-      <c r="U1" s="22" t="n"/>
-      <c r="V1" s="22" t="n"/>
-      <c r="W1" s="22" t="n"/>
-      <c r="X1" s="22" t="n"/>
-      <c r="Y1" s="22" t="n"/>
-      <c r="Z1" s="22" t="n"/>
-      <c r="AA1" s="22" t="n"/>
+      <c r="Y1" s="24" t="n"/>
+      <c r="Z1" s="24" t="n"/>
+      <c r="AA1" s="24" t="n"/>
+      <c r="AB1" s="24" t="n"/>
+      <c r="AC1" s="24" t="n"/>
+      <c r="AD1" s="24" t="n"/>
+      <c r="AE1" s="24" t="n"/>
+      <c r="AF1" s="24" t="n"/>
+      <c r="AG1" s="24" t="n"/>
+      <c r="AH1" s="24" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="21" t="n">
         <v>101774195</v>
       </c>
-      <c r="B2" s="11" t="n"/>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>deborshi.som@pwc.com</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Deborshi Som</t>
@@ -1872,25 +1925,64 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O2" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P2" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
+      <c r="O2" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P2" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R2" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S2" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T2" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U2" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="21" t="n">
         <v>101675341</v>
       </c>
-      <c r="B3" s="11" t="n"/>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>abhinandan.roy@pwc.com</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Abhinandan Roy</t>
@@ -1946,18 +2038,53 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="O3" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P3" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>12</v>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P3" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q3" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S3" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U3" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W3" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2157,42 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2094,7 +2256,7 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2104,8 +2266,43 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q5" t="n">
-        <v>6</v>
+      <c r="Q5" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S5" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U5" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2168,21 +2365,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z6" s="16" t="n"/>
-      <c r="AA6" s="16" t="n"/>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U6" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V6" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -2254,11 +2486,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="16" t="n"/>
-      <c r="AA7" s="16" t="n"/>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T7" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U7" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG7" s="16" t="n"/>
+      <c r="AH7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
@@ -2320,21 +2587,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z8" s="16" t="n"/>
-      <c r="AA8" s="16" t="n"/>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S8" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W8" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG8" s="16" t="n"/>
+      <c r="AH8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -2396,7 +2698,7 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2406,11 +2708,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="16" t="n"/>
+      <c r="Q9" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S9" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W9" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG9" s="16" t="n"/>
+      <c r="AH9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
@@ -2477,16 +2814,51 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z10" s="16" t="n"/>
-      <c r="AA10" s="16" t="n"/>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q10" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R10" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T10" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U10" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" s="16" t="n"/>
+      <c r="AH10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -2548,21 +2920,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O11" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="16" t="n"/>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S11" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="16" t="n"/>
+      <c r="AH11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
@@ -2624,21 +3031,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q12" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S12" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U12" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG12" s="16" t="n"/>
+      <c r="AH12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n">
@@ -2709,7 +3151,7 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2719,11 +3161,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="16" t="n"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T13" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U13" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W13" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" s="16" t="n"/>
+      <c r="AH13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
@@ -2794,21 +3271,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O14" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z14" s="16" t="n"/>
-      <c r="AA14" s="16" t="n"/>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T14" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U14" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="16" t="n"/>
+      <c r="AH14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
@@ -2879,7 +3391,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O15" s="23" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2889,11 +3401,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z15" s="16" t="n"/>
-      <c r="AA15" s="16" t="n"/>
+      <c r="Q15" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S15" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T15" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U15" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" s="16" t="n"/>
+      <c r="AH15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
@@ -2964,21 +3511,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O16" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="16" t="n"/>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S16" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T16" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="16" t="n"/>
+      <c r="AH16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n">
@@ -3049,21 +3631,56 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="O17" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="P17" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="16" t="n"/>
-      <c r="AA17" s="16" t="n"/>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q17" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="S17" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T17" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="16" t="n"/>
+      <c r="AH17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n">
@@ -3144,11 +3761,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="16" t="n"/>
-      <c r="AA18" s="16" t="n"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="16" t="n"/>
+      <c r="AH18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n">
@@ -3224,16 +3876,51 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="P19" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z19" s="16" t="n"/>
-      <c r="AA19" s="16" t="n"/>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S19" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T19" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W19" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG19" s="16" t="n"/>
+      <c r="AH19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -3309,16 +3996,51 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
         <v>5</v>
       </c>
-      <c r="Z20" s="16" t="n"/>
-      <c r="AA20" s="16" t="n"/>
+      <c r="AG20" s="16" t="n"/>
+      <c r="AH20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -3399,11 +4121,46 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="16" t="n"/>
-      <c r="AA21" s="16" t="n"/>
+      <c r="Q21" s="20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S21" s="23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="T21" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="16" t="n"/>
+      <c r="AH21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -3484,1049 +4241,3160 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
         <v>2</v>
       </c>
-      <c r="Z22" s="16" t="n"/>
-      <c r="AA22" s="16" t="n"/>
+      <c r="AG22" s="16" t="n"/>
+      <c r="AH22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="16" t="n"/>
-      <c r="AA23" s="16" t="n"/>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="16" t="n"/>
+      <c r="AH23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="16" t="n"/>
-      <c r="AA24" s="16" t="n"/>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="16" t="n"/>
+      <c r="AH24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="S26" s="23" t="n"/>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="R32" s="23" t="n"/>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="23" t="n"/>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="R40" s="23" t="n"/>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="R42" s="23" t="n"/>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="R43" s="23" t="n"/>
+      <c r="S43" s="23" t="n"/>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="M45" s="19" t="n"/>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="M47" s="19" t="n"/>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="M49" s="19" t="n"/>
+      <c r="N49" s="19" t="n"/>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="M51" s="19" t="n"/>
+      <c r="N51" s="19" t="n"/>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="M52" s="19" t="n"/>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="M53" s="19" t="n"/>
+      <c r="N53" s="19" t="n"/>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="M56" s="19" t="n"/>
+      <c r="N56" s="19" t="n"/>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>101588348</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Oindrila Chakraborty</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>101582442</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Subhabrata Sengupta</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>101578754</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ishita Banerjee</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>101560450</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Anusree Roy</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>101560255</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Kumari Ritul</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W61" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>101453747</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Moupriya Ganguly</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>101442680</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Ratul Ghosh</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>101442606</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Avisake Chowdhury</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>101442577</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Banavathu Naik</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>101442457</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Piyush Deb</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>101442398</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Shreya Singh</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>101408941</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Riya Biswas</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>101282639</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Soumya Mondal</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>101259073</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Sayanti Pal</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>101148869</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Arunabha Mitra</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>101110378</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Solanki Kundu</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>100682010</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Nazia Afreen</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>101752092</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Madhu Komera</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>101675381</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Venkatesh Ulla</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W75" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>101699107</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>ANKIT Mahali</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>101264925</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Ritwik Acharya</t>
         </is>
       </c>
-      <c r="M45" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>101560676</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>REDDI KEERTHI</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>101560510</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Anik Tanzim</t>
-        </is>
-      </c>
-      <c r="M47" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>101442923</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ayantik Das</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>101744590</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Sunirmal Bera</t>
-        </is>
-      </c>
-      <c r="M49" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N49" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>101758893</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ankita Chhetry</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>101675169</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Vikash Kumar</t>
-        </is>
-      </c>
-      <c r="M51" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N51" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>101743106</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Rishagny Choudhury</t>
-        </is>
-      </c>
-      <c r="M52" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>101777658</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Kaustav Chakraborty</t>
-        </is>
-      </c>
-      <c r="M53" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N53" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>101774195</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Deborshi Som</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>101779334</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SAQLAIN Mustafa</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>101675341</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Abhinandan Roy</t>
-        </is>
-      </c>
-      <c r="M56" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="N56" s="19" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="mailto:n.jyotheeswar@pwc.com" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="mailto:abhinav.baranwal@pwc.com" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="mailto:mukul.z.kumar@pwc.com" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="mailto:ishwar.jha@pwc.com" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="mailto:vivek.nayak@pwc.com" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="mailto:aditi.khaitan@pwc.com" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="mailto:sumit.m.shaw@pwc.com" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="mailto:debojyoti.s.saha@pwc.com" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="mailto:gourab.x.das@pwc.com" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="mailto:tushti.thakur@pwc.com" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="mailto:n.jyotheeswar@pwc.com" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="mailto:abhinav.baranwal@pwc.com" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="mailto:mukul.z.kumar@pwc.com" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="mailto:ishwar.jha@pwc.com" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="mailto:vivek.nayak@pwc.com" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="mailto:aditi.khaitan@pwc.com" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="mailto:sumit.m.shaw@pwc.com" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="mailto:debojyoti.s.saha@pwc.com" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="mailto:gourab.x.das@pwc.com" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="mailto:tushti.thakur@pwc.com" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>101588348</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oindrila Chakraborty</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>101582442</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Subhabrata Sengupta</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>101578754</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ishita Banerjee</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>101560676</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>REDDI KEERTHI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>101560510</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Anik Tanzim</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>101560450</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Anusree Roy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>101560255</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kumari Ritul</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>101453747</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moupriya Ganguly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>101442923</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ayantik Das</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>101442680</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ratul Ghosh</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>101442606</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avisake Chowdhury</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>101442577</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banavathu Naik</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>101442457</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Piyush Deb</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>101442398</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Shreya Singh</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>101408941</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Riya Biswas</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>101282639</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Soumya Mondal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>101259073</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sayanti Pal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>101148869</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arunabha Mitra</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>101110378</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Solanki Kundu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>101744590</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sunirmal Bera</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>101758893</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ankita Chhetry</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>101675169</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vikash Kumar</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>101743106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rishagny Choudhury</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>101777658</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kaustav Chakraborty</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>101774195</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Deborshi Som</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>101779334</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SAQLAIN Mustafa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>100682010</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nazia Afreen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>101752092</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Madhu Komera</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>101675381</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Venkatesh Ulla</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>101786698</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>N Jyotheeswar</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>101699107</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ANKIT Mahali</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>101264925</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ritwik Acharya</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>101675401</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Abhinav Baranwal</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>101755619</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mukul Kumar</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>101675341</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Abhinandan Roy</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>101787312</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ISHWAR Jha</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I37" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>101775278</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vivek Nayak</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="I38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>101082599</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Aditi Khaitan</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>101807073</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sumit Shaw</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>101790824</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Debojyoti Saha</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>101805990</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gourab Das</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>101676413</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tushti Thakur</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>